--- a/BOM Format/Client.Bom.Template.xlsx
+++ b/BOM Format/Client.Bom.Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\BOM Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A084152F-FB2A-4F62-9B18-304A6CE942AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7285DD1E-4027-4950-AD4F-466F2BD1F68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -214,7 +214,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -235,12 +235,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -473,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -547,10 +541,10 @@
     <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -573,12 +567,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -618,10 +606,10 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1003,15 +991,15 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
     </row>
     <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="23"/>
-      <c r="C2" s="48"/>
+      <c r="C2" s="46"/>
       <c r="D2" s="10" t="s">
         <v>0</v>
       </c>
@@ -1025,12 +1013,12 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="45"/>
+      <c r="M2" s="43"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="24"/>
-      <c r="C3" s="49"/>
+      <c r="C3" s="47"/>
       <c r="D3" s="12" t="s">
         <v>2</v>
       </c>
@@ -1044,12 +1032,12 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
-      <c r="M3" s="59"/>
+      <c r="M3" s="57"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="24"/>
-      <c r="C4" s="49"/>
+      <c r="C4" s="47"/>
       <c r="D4" s="12" t="s">
         <v>4</v>
       </c>
@@ -1063,12 +1051,12 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
-      <c r="M4" s="60"/>
+      <c r="M4" s="58"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="24"/>
-      <c r="C5" s="49"/>
+      <c r="C5" s="47"/>
       <c r="D5" s="12" t="s">
         <v>6</v>
       </c>
@@ -1082,12 +1070,12 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="60"/>
+      <c r="M5" s="58"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="25"/>
-      <c r="C6" s="50"/>
+      <c r="C6" s="48"/>
       <c r="D6" s="18"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
@@ -1097,12 +1085,12 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="60"/>
+      <c r="M6" s="58"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="26"/>
-      <c r="C7" s="51"/>
+      <c r="C7" s="49"/>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
       <c r="F7" s="21"/>
@@ -1112,12 +1100,12 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="60"/>
+      <c r="M7" s="58"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="29"/>
-      <c r="C8" s="52"/>
+      <c r="C8" s="50"/>
       <c r="D8" s="30"/>
       <c r="E8" s="30"/>
       <c r="F8" s="31"/>
@@ -1127,7 +1115,7 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-      <c r="M8" s="60"/>
+      <c r="M8" s="58"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1161,7 +1149,7 @@
       <c r="K9" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="56" t="s">
+      <c r="L9" s="54" t="s">
         <v>17</v>
       </c>
       <c r="M9" s="32" t="s">
@@ -1170,7 +1158,7 @@
     </row>
     <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="55">
+      <c r="B10" s="53">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
@@ -1191,7 +1179,7 @@
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="55">
+      <c r="B11" s="53">
         <f t="shared" ref="B11:B12" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
@@ -1212,29 +1200,29 @@
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="55">
+      <c r="B12" s="53">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C12" s="39"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="43"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="41"/>
       <c r="L12" s="40">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M12" s="57"/>
+      <c r="M12" s="55"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="34"/>
-      <c r="C13" s="53"/>
+      <c r="C13" s="51"/>
       <c r="D13" s="35"/>
       <c r="E13" s="36"/>
       <c r="F13" s="37"/>
@@ -1244,12 +1232,12 @@
       <c r="J13" s="38"/>
       <c r="K13" s="38"/>
       <c r="L13" s="38"/>
-      <c r="M13" s="46"/>
+      <c r="M13" s="44"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="54"/>
+      <c r="C14" s="52"/>
       <c r="D14" s="8"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
@@ -1259,7 +1247,7 @@
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
-      <c r="M14" s="47"/>
+      <c r="M14" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/BOM Format/Client.Bom.Template.xlsx
+++ b/BOM Format/Client.Bom.Template.xlsx
@@ -1,50 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\eSpark-Hardware\BOM Format\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\eSpark-Hardware\BOM Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7285DD1E-4027-4950-AD4F-466F2BD1F68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>Component list</t>
-  </si>
-  <si>
-    <t>Field=Title</t>
-  </si>
-  <si>
-    <t>Source Data From:</t>
-  </si>
-  <si>
-    <t>Field=DataSourceFileName</t>
-  </si>
-  <si>
-    <t>Project:</t>
-  </si>
-  <si>
-    <t>Field=ProjectFileName</t>
-  </si>
-  <si>
-    <t>Variant:</t>
-  </si>
-  <si>
-    <t>Field=VariantName</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>#</t>
   </si>
@@ -73,23 +48,14 @@
     <t>Column=Remarks</t>
   </si>
   <si>
-    <t>Column=Quantity (5 Boards)</t>
-  </si>
-  <si>
     <t>Column=Item Type</t>
-  </si>
-  <si>
-    <t>Column=Alternate Part Number</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-  </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,58 +66,6 @@
     <font>
       <sz val="10"/>
       <color indexed="13"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color indexed="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -178,29 +92,6 @@
     </font>
     <font>
       <b/>
-      <sz val="24"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -209,6 +100,13 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -240,7 +138,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -259,29 +157,9 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -307,15 +185,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -349,19 +218,6 @@
     <border>
       <left/>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -439,19 +295,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -467,162 +310,89 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -645,60 +415,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>19942</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>1905000</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20059650" y="629542"/>
-          <a:ext cx="1857375" cy="1104008"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -963,299 +679,148 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="28" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.42578125" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="29.42578125" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
     </row>
-    <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11" t="s">
+      <c r="C2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="43"/>
+      <c r="F2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="12" t="s">
+      <c r="B3" s="23">
+        <f>ROW(B3) - ROW($B$2)</f>
+        <v>1</v>
+      </c>
+      <c r="C3" s="26"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="23">
+        <f t="shared" ref="B4:B5" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="57"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="58"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="58"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="58"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="58"/>
-    </row>
-    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="58"/>
-    </row>
-    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="L9" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="M9" s="32" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="53">
-        <f>ROW(B10) - ROW($B$9)</f>
-        <v>1</v>
-      </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="40">
-        <f>K10*5</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="39"/>
-    </row>
-    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="53">
-        <f t="shared" ref="B11:B12" si="0">ROW(B11) - ROW($B$9)</f>
-        <v>2</v>
-      </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="42"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="42">
-        <f t="shared" ref="L11:L12" si="1">K11*5</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="41"/>
-    </row>
-    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="53">
+      <c r="B5" s="23">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="41"/>
-      <c r="L12" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="55"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="24"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="44"/>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="19"/>
     </row>
-    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="45"/>
+    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="M3:M8"/>
+  <mergeCells count="1">
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/BOM Format/Client.Bom.Template.xlsx
+++ b/BOM Format/Client.Bom.Template.xlsx
@@ -55,7 +55,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,19 +71,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -112,7 +99,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -127,18 +114,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF03A4CB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -159,15 +140,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -186,52 +158,10 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -281,7 +211,24 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -292,12 +239,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -310,88 +253,53 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -681,11 +589,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
@@ -698,123 +606,97 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="23">
+      <c r="B3" s="11">
         <f>ROW(B3) - ROW($B$2)</f>
         <v>1</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
-      <c r="B4" s="23">
+      <c r="B4" s="11">
         <f t="shared" ref="B4:B5" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="23">
+      <c r="B5" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="24"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="19"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="20"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
